--- a/data/questionnaires/vsq-a.xlsx
+++ b/data/questionnaires/vsq-a.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -801,26 +801,26 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VSQ-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Can your customers sign in to your product through single sign-on with their own identity provider?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>DATA SECURITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>VSQ-16</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Data Security</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Is customer data encrypted at rest in your production environment?</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Do you encrypt customer data in transit using TLS 1.2 or higher?</t>
+          <t>Is customer data encrypted at rest in your production environment?</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Are your encryption keys rotated at least annually?</t>
+          <t>Do you encrypt customer data in transit using TLS 1.2 or higher?</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Do you have a data classification scheme that assigns each type of data you handle a sensitivity level?</t>
+          <t>Are your encryption keys rotated at least annually?</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Do you delete customer data within 30 days after a contract ends?</t>
+          <t>Do you have a data classification scheme that assigns each type of data you handle a sensitivity level?</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Is ALL customer data stored in AWS, with nothing held on premises?</t>
+          <t>Do you delete customer data within 30 days after a contract ends?</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Do you use customer data to train machine learning models?</t>
+          <t>Is ALL customer data stored in AWS, with nothing held on premises?</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Do you require full-disk encryption on all company laptops?</t>
+          <t>Do you use customer data to train machine learning models?</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Do you wipe or destroy storage media that held unencrypted production data before it is reused or disposed of?</t>
+          <t>Do you require full-disk encryption on all company laptops?</t>
         </is>
       </c>
     </row>
@@ -973,31 +973,31 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
+          <t>Do you wipe or physically destroy the storage media of retired assets before they are reused or disposed of?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>VSQ-26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Data Security</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
           <t>Do you keep a current diagram of how sensitive data enters your systems and where it is stored?</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>BUSINESS CONTINUITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>VSQ-26</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Business Continuity</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Are your production databases backed up at least daily?</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Do you test restoring from your backups at least quarterly?</t>
+          <t>Are your production databases backed up at least daily?</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Have you defined recovery time and recovery point objectives for your production service?</t>
+          <t>Do you test restoring from your backups at least quarterly?</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Do you test failover to your disaster recovery setup at least annually?</t>
+          <t>Have you defined recovery time and recovery point objectives for your production service?</t>
         </is>
       </c>
     </row>
@@ -1065,31 +1065,31 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
+          <t>Do you test failover to your disaster recovery setup at least annually?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VSQ-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Business Continuity</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
           <t>Do you run a trial restore from backup at least quarterly to prove that the backups work?</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>VULNERABILITY MANAGEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>VSQ-31</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Vulnerability Management</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Do you regularly scan your production systems for known vulnerabilities?</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Do you patch critical vulnerabilities within 30 days of discovery?</t>
+          <t>Do you regularly scan your production systems for known vulnerabilities?</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Does an independent third party penetration test your product at least annually?</t>
+          <t>Do you patch critical vulnerabilities within 30 days of discovery?</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Have the findings from your most recent penetration test been remediated?</t>
+          <t>Does an independent third party penetration test your product at least annually?</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Do you run a public bug bounty program that rewards outside researchers for reporting vulnerabilities?</t>
+          <t>Have the findings from your most recent penetration test been remediated?</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Do you give outside researchers an easy-to-find way to report security vulnerabilities, such as a published disclosure policy?</t>
+          <t>Do you run a public bug bounty program that rewards outside researchers for reporting vulnerabilities?</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Do you run dynamic application security testing (DAST) against your running application?</t>
+          <t>Do you give outside researchers a published way to report security vulnerabilities and acknowledge their reports within a set time?</t>
         </is>
       </c>
     </row>
@@ -1208,31 +1208,31 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
+          <t>Do you run dynamic application security testing (DAST) against your running application?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VSQ-39</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Vulnerability Management</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
           <t>Are customers allowed to run their own penetration tests against your product?</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>SECURE DEVELOPMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>VSQ-39</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Secure Development</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Do you run static application security testing (SAST) on your source code?</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Does a second engineer review every code change before it is merged?</t>
+          <t>Do you run static application security testing (SAST) on your source code?</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Does your web application set security headers, such as a Content Security Policy and framing restrictions?</t>
+          <t>Does a second engineer review every code change before it is merged?</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Is your application built on maintained frameworks that escape output and sanitize input automatically?</t>
+          <t>Does your web application set security headers, such as a Content Security Policy and framing restrictions?</t>
         </is>
       </c>
     </row>
@@ -1300,48 +1300,48 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Are releases built from version control by a consistent build process that records how each artifact was built?</t>
+          <t>Do your developers rely on their framework's built-in protections for input validation and output encoding?</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>INCIDENT RESPONSE</t>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VSQ-44</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Secure Development</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Do production builds and deployments run only through an automated CI/CD pipeline?</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VSQ-44</t>
+          <t>VSQ-45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Incident Response</t>
+          <t>Secure Development</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Do you have a documented incident response plan?</t>
+          <t>Do you train your developers to prevent common web vulnerabilities, such as authorization bypass, injection and cross-site scripting?</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>VSQ-45</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Incident Response</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Do you hold an incident response tabletop exercise at least annually?</t>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>INCIDENT RESPONSE</t>
         </is>
       </c>
     </row>
@@ -1358,130 +1358,130 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Do you notify affected customers within 72 hours of confirming a security breach?</t>
+          <t>Do you have a documented incident response plan?</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>VENDOR MANAGEMENT</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VSQ-47</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Incident Response</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Do you hold an incident response tabletop exercise at least annually?</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VSQ-47</t>
+          <t>VSQ-48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>Incident Response</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Do you notify affected customers within 72 hours of confirming a security breach?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>VENDOR MANAGEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VSQ-49</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Vendor Management</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Do you assess the security risk of each vendor at least annually?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>VSQ-48</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Vendor Management</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Do you keep a list of your subprocessors and give customers advance notice before adding a new one?</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>HUMAN RESOURCES</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VSQ-49</t>
+          <t>VSQ-50</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>Vendor Management</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Do you keep a list of your subprocessors and give customers advance notice before adding a new one?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>HUMAN RESOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VSQ-51</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Human Resources</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Do you run background checks on all personnel, employees and contractors alike, before they access sensitive systems?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>VSQ-50</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Human Resources</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Do all employees complete security awareness training at least annually?</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>LOGGING AND MONITORING</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VSQ-51</t>
+          <t>VSQ-52</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Logging and Monitoring</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Do you retain security logs for at least 12 months?</t>
+          <t>Do all employees complete security awareness training at least annually?</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>VSQ-52</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Logging and Monitoring</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Are security logs from your systems collected in a central location?</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>LOGGING AND MONITORING</t>
         </is>
       </c>
     </row>
@@ -1498,89 +1498,89 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Do security events generate alerts to your on-call staff?</t>
+          <t>Do you retain security logs for at least 12 months?</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>ASSET MANAGEMENT</t>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VSQ-54</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Logging and Monitoring</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Are security logs from your systems collected in a central location?</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VSQ-54</t>
+          <t>VSQ-55</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>Logging and Monitoring</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Do security events generate alerts to your on-call staff?</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>ASSET MANAGEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VSQ-56</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>Asset Management</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Do you maintain an inventory of your information assets, such as servers, laptops and cloud accounts?</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>VSQ-55</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Asset Management</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Is ALL infrastructure behind your service hosted in AWS, with nothing on premises?</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>ENGAGEMENT</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VSQ-56</t>
+          <t>VSQ-57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Does your company carry cyber insurance that would cover a security incident involving Northbeam Health's data?</t>
+          <t>Is ALL infrastructure behind your service hosted in AWS, with nothing on premises?</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>VSQ-57</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>Is the coverage limit of your cyber insurance at least USD 5,000,000 per claim?</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>ENGAGEMENT</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Will you name a security contact for Northbeam Health's account, with name, email address and a 24/7 phone number?</t>
+          <t>Does your company carry cyber insurance that would cover a security incident involving Northbeam Health's data?</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Will you name the person Northbeam Health should call first if a security incident affects its data, with name, email address and phone number?</t>
+          <t>Is the coverage limit of your cyber insurance at least USD 5,000,000 per claim?</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Does your service let Northbeam Health use customer-managed encryption keys for its data?</t>
+          <t>Will you designate a security contact for Northbeam Health's account and provide that person's name, email address and a 24/7 phone number?</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Will your contract with Northbeam Health include an uptime SLA of at least 99.9%?</t>
+          <t>Will you designate an incident contact for Northbeam Health's account and provide that person's name, email address and a 24/7 phone number?</t>
         </is>
       </c>
     </row>
@@ -1665,27 +1665,61 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
+          <t>Does your service let Northbeam Health use customer-managed encryption keys for its data?</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>VSQ-63</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Will your contract with Northbeam Health include an uptime SLA of at least 99.9%?</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VSQ-64</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
           <t>Will you share your latest penetration test report with Northbeam Health under an NDA?</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D7 D8 D9 D10 D11 D12 D14 D15 D16 D17 D18 D19 D20 D21 D22 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D35 D36 D37 D38 D39 D41 D42 D43 D44 D45 D46 D47 D48 D50 D51 D52 D53 D54 D56 D57 D58 D60 D61 D63 D64 D66 D67 D68 D70 D71 D73 D74 D75 D76 D77 D78 D79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D7 D8 D9 D10 D11 D12 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D42 D43 D44 D45 D46 D47 D48 D49 D51 D52 D53 D54 D55 D56 D58 D59 D60 D62 D63 D65 D66 D68 D69 D70 D72 D73 D75 D76 D77 D78 D79 D80 D81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No,N/A"</formula1>
     </dataValidation>
   </dataValidations>
